--- a/AppLogSolutionLocale/dati/tabella_aggiornamento_articoli.xlsx
+++ b/AppLogSolutionLocale/dati/tabella_aggiornamento_articoli.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\App\AppLogSolution\dati\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\App\AppLogSolutionLocale\dati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA724D3-F05A-4207-8624-A55C46713140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EB05FBD-91F6-430B-B66A-C798A62CC647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Articoli" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="119">
   <si>
     <t>Codice</t>
   </si>
@@ -64,9 +64,6 @@
     <t>10-GEL</t>
   </si>
   <si>
-    <t>Buste ghiaccio gel (Data)</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
@@ -208,9 +205,6 @@
     <t>ME-S-BI-L3-NA</t>
   </si>
   <si>
-    <t>10-FLYER Codice: --300326</t>
-  </si>
-  <si>
     <t>SPECIALE 2 Finocchio biologico da porzionare in classe</t>
   </si>
   <si>
@@ -226,9 +220,6 @@
     <t>37 Porzioni / Collo</t>
   </si>
   <si>
-    <t>Flyer programma</t>
-  </si>
-  <si>
     <t>FR-M-BI-L3-NI</t>
   </si>
   <si>
@@ -316,9 +307,6 @@
     <t>19</t>
   </si>
   <si>
-    <t>Mela di Val di Non DOP</t>
-  </si>
-  <si>
     <t>100</t>
   </si>
   <si>
@@ -337,9 +325,6 @@
     <t>16</t>
   </si>
   <si>
-    <t>Pera dell Emilia Romagna Igp</t>
-  </si>
-  <si>
     <t>LT-AQ-04-LB</t>
   </si>
   <si>
@@ -377,6 +362,24 @@
   </si>
   <si>
     <t>7.14</t>
+  </si>
+  <si>
+    <t>AL-M-BI-L3-NI</t>
+  </si>
+  <si>
+    <t>Mousse di Albicocca biologica (Data)</t>
+  </si>
+  <si>
+    <t>24 Porzioni / Collo</t>
+  </si>
+  <si>
+    <t>SUCCO-REC</t>
+  </si>
+  <si>
+    <t>Succo di frutta (Data)</t>
+  </si>
+  <si>
+    <t>Buste ghiaccio gel</t>
   </si>
 </sst>
 </file>
@@ -733,7 +736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.36328125" customWidth="1"/>
@@ -775,44 +778,44 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -834,564 +837,568 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
       <c r="H6" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="A8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="B9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="1">
+        <v>24</v>
+      </c>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" t="s">
         <v>87</v>
       </c>
-      <c r="B9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="1">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="1">
-        <v>24</v>
-      </c>
-      <c r="H10" s="4"/>
+      <c r="C10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>95</v>
+        <v>61</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="H11" s="3">
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="C12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F12" s="1"/>
-      <c r="H12" s="3">
-        <v>48</v>
+        <v>98</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>91</v>
-      </c>
-      <c r="B13" t="s">
-        <v>101</v>
-      </c>
-      <c r="C13" t="s">
-        <v>102</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>103</v>
+      <c r="A13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="4" t="s">
-        <v>26</v>
+      <c r="A14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" t="s">
+        <v>67</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>68</v>
+      <c r="A15" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" t="s">
         <v>77</v>
       </c>
-      <c r="B16" t="s">
-        <v>78</v>
-      </c>
-      <c r="C16" t="s">
-        <v>80</v>
-      </c>
       <c r="H16" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B17" t="s">
-        <v>79</v>
-      </c>
-      <c r="C17" t="s">
-        <v>80</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>30</v>
+      <c r="A17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="4" t="s">
-        <v>30</v>
+      <c r="A18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" t="s">
+        <v>90</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>96</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="A20" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" t="s">
         <v>72</v>
       </c>
-      <c r="B20" t="s">
-        <v>74</v>
-      </c>
       <c r="C20" t="s">
+        <v>28</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>30</v>
-      </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="5" t="s">
-        <v>73</v>
+      <c r="A21" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" t="s">
-        <v>29</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>30</v>
+        <v>101</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="1">
+        <v>1</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21">
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B22" t="s">
-        <v>106</v>
+        <v>103</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G22">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>108</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>107</v>
-      </c>
       <c r="D23" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G23">
-        <v>10</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="G23" s="1">
+        <v>6</v>
+      </c>
+      <c r="H23" s="4"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>106</v>
+        <v>34</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" s="1">
-        <v>1</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G24" s="1">
-        <v>6</v>
-      </c>
-      <c r="H24" s="4"/>
+        <v>35</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="4" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="4" t="s">
-        <v>37</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" s="1">
+        <v>10</v>
+      </c>
+      <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G26" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H26" s="4"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E27" s="1">
-        <v>1</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G27" s="1">
-        <v>6</v>
-      </c>
-      <c r="H27" s="4"/>
+        <v>43</v>
+      </c>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="4" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D28" s="1"/>
+      <c r="A28" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" t="s">
+        <v>64</v>
+      </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="4" t="s">
+      <c r="H28" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>60</v>
-      </c>
-      <c r="B29" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" t="s">
-        <v>66</v>
-      </c>
+      <c r="B29" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
-      <c r="H29" s="3" t="s">
-        <v>65</v>
+      <c r="G29" s="1"/>
+      <c r="H29" s="4" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="4" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>46</v>
-      </c>
-      <c r="B31" t="s">
-        <v>97</v>
-      </c>
-      <c r="C31" t="s">
-        <v>48</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>49</v>
-      </c>
+      <c r="A31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="1">
+        <v>1</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
+      <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="4" t="s">
-        <v>11</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" s="1">
+        <v>1</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" s="1">
+        <v>6</v>
+      </c>
+      <c r="H32" s="4"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="B33" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C33" t="s">
-        <v>52</v>
+        <v>111</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>11</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34" s="1">
-        <v>1</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G34" s="1">
-        <v>10</v>
-      </c>
-      <c r="H34" s="4"/>
+      <c r="A34" t="s">
+        <v>108</v>
+      </c>
+      <c r="B34" t="s">
+        <v>109</v>
+      </c>
+      <c r="C34" t="s">
+        <v>64</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>58</v>
+      <c r="A35" t="s">
+        <v>113</v>
+      </c>
+      <c r="B35" t="s">
+        <v>114</v>
+      </c>
+      <c r="C35" t="s">
+        <v>67</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G35" s="1">
-        <v>6</v>
-      </c>
-      <c r="H35" s="4"/>
+        <v>10</v>
+      </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B36" t="s">
+        <v>117</v>
+      </c>
+      <c r="C36" t="s">
         <v>115</v>
       </c>
-      <c r="C36" t="s">
-        <v>116</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>113</v>
-      </c>
-      <c r="B37" t="s">
-        <v>114</v>
-      </c>
-      <c r="C37" t="s">
-        <v>66</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>65</v>
+      <c r="D36" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="1">
+        <v>1</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G36" s="1">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/AppLogSolutionLocale/dati/tabella_aggiornamento_articoli.xlsx
+++ b/AppLogSolutionLocale/dati/tabella_aggiornamento_articoli.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\App\AppLogSolutionLocale\dati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EB05FBD-91F6-430B-B66A-C798A62CC647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C05690-0AEB-4D5E-B199-183EFCFD7D06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Articoli" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="126">
   <si>
     <t>Codice</t>
   </si>
@@ -380,6 +380,28 @@
   </si>
   <si>
     <t>Buste ghiaccio gel</t>
+  </si>
+  <si>
+    <t>PF-T-LI-L3-NA</t>
+  </si>
+  <si>
+    <t>SU-M-BI-L3-NI</t>
+  </si>
+  <si>
+    <t>Mirtillo Tal quale (Data)</t>
+  </si>
+  <si>
+    <t>8 Porzioni / Collo</t>
+  </si>
+  <si>
+    <t>Mousse biologica di Susina (Data)</t>
+  </si>
+  <si>
+    <t>YO-CN-MN-04-
+LB</t>
+  </si>
+  <si>
+    <t>Yogurt naturale bianco intero (Data)</t>
   </si>
 </sst>
 </file>
@@ -736,7 +758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.36328125" customWidth="1"/>
@@ -1401,6 +1423,75 @@
         <v>24</v>
       </c>
     </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>119</v>
+      </c>
+      <c r="B37" t="s">
+        <v>121</v>
+      </c>
+      <c r="C37" t="s">
+        <v>122</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" s="1">
+        <v>1</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G37" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>120</v>
+      </c>
+      <c r="B38" t="s">
+        <v>123</v>
+      </c>
+      <c r="C38" t="s">
+        <v>47</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G38" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>124</v>
+      </c>
+      <c r="B39" t="s">
+        <v>125</v>
+      </c>
+      <c r="C39" t="s">
+        <v>105</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" s="1">
+        <v>1</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G39" s="1">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H35">

--- a/AppLogSolutionLocale/dati/tabella_aggiornamento_articoli.xlsx
+++ b/AppLogSolutionLocale/dati/tabella_aggiornamento_articoli.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\App\AppLogSolutionLocale\dati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C05690-0AEB-4D5E-B199-183EFCFD7D06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA795717-8B57-409A-A735-4DFF177DCC3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Articoli" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="129">
   <si>
     <t>Codice</t>
   </si>
@@ -402,6 +402,15 @@
   </si>
   <si>
     <t>Yogurt naturale bianco intero (Data)</t>
+  </si>
+  <si>
+    <t>AL-T-LI-NA</t>
+  </si>
+  <si>
+    <t>Albicocca tal quale</t>
+  </si>
+  <si>
+    <t>12 Porzioni / Collo</t>
   </si>
 </sst>
 </file>
@@ -758,11 +767,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H39"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H40"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.36328125" customWidth="1"/>
-    <col min="2" max="2" width="47.90625" customWidth="1"/>
+    <col min="1" max="1" width="28.33203125" customWidth="1"/>
+    <col min="2" max="2" width="47.88671875" customWidth="1"/>
     <col min="3" max="3" width="38" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
@@ -772,7 +781,7 @@
     <col min="9" max="9" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -798,35 +807,39 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
-        <v>79</v>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>82</v>
       </c>
@@ -840,179 +853,208 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" t="s">
+        <v>96</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>19</v>
+        <v>100</v>
+      </c>
+      <c r="B9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>102</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" s="1">
-        <v>24</v>
-      </c>
-      <c r="H9" s="4"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B10" t="s">
-        <v>87</v>
-      </c>
-      <c r="C10" t="s">
-        <v>91</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" t="s">
-        <v>61</v>
-      </c>
-      <c r="F11" s="1"/>
-      <c r="H11" s="3">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>88</v>
-      </c>
-      <c r="B12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" t="s">
-        <v>98</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+        <v>32</v>
+      </c>
+      <c r="G9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="1">
+        <v>6</v>
+      </c>
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B14" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" t="s">
-        <v>67</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+        <v>106</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="1">
+        <v>6</v>
+      </c>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
         <v>77</v>
@@ -1021,72 +1063,80 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16" t="s">
-        <v>77</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>89</v>
-      </c>
-      <c r="B18" t="s">
-        <v>87</v>
-      </c>
-      <c r="C18" t="s">
-        <v>90</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>69</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B20" t="s">
         <v>71</v>
-      </c>
-      <c r="C19" t="s">
-        <v>28</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20" t="s">
-        <v>72</v>
       </c>
       <c r="C20" t="s">
         <v>28</v>
@@ -1095,275 +1145,231 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B21" t="s">
-        <v>101</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="1">
-        <v>1</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>102</v>
+        <v>45</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>119</v>
+      </c>
+      <c r="B22" t="s">
+        <v>121</v>
+      </c>
+      <c r="C22" t="s">
+        <v>122</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G22">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" s="1">
+        <v>21</v>
+      </c>
+      <c r="G22" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" t="s">
+        <v>67</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24" t="s">
+        <v>123</v>
+      </c>
+      <c r="C24" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="1">
         <v>1</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G23" s="1">
-        <v>6</v>
-      </c>
-      <c r="H23" s="4"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>106</v>
+      <c r="F24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>113</v>
+      </c>
+      <c r="B25" t="s">
+        <v>114</v>
+      </c>
+      <c r="C25" t="s">
+        <v>67</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G25" s="1">
         <v>10</v>
       </c>
-      <c r="H25" s="4"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E26" s="1">
-        <v>1</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G26" s="1">
-        <v>6</v>
-      </c>
-      <c r="H26" s="4"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A27" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>59</v>
-      </c>
-      <c r="B28" t="s">
-        <v>62</v>
-      </c>
-      <c r="C28" t="s">
-        <v>64</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" t="s">
+        <v>28</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
-      <c r="H28" s="3" t="s">
+      <c r="G28" s="1"/>
+      <c r="H28" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" t="s">
+        <v>91</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>89</v>
+      </c>
+      <c r="B30" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" t="s">
+        <v>90</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>107</v>
+      </c>
+      <c r="B31" t="s">
+        <v>110</v>
+      </c>
+      <c r="C31" t="s">
+        <v>111</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" t="s">
+        <v>61</v>
+      </c>
+      <c r="F32" s="1"/>
+      <c r="H32" s="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33" t="s">
+        <v>64</v>
+      </c>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="H33" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A31" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="1">
-        <v>1</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G31" s="1">
-        <v>10</v>
-      </c>
-      <c r="H31" s="4"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A32" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E32" s="1">
-        <v>1</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32" s="1">
-        <v>6</v>
-      </c>
-      <c r="H32" s="4"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>107</v>
-      </c>
-      <c r="B33" t="s">
-        <v>110</v>
-      </c>
-      <c r="C33" t="s">
-        <v>111</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>108</v>
       </c>
@@ -1377,15 +1383,15 @@
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B35" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C35" t="s">
-        <v>67</v>
+        <v>115</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>20</v>
@@ -1397,18 +1403,18 @@
         <v>21</v>
       </c>
       <c r="G35" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>116</v>
-      </c>
-      <c r="B36" t="s">
-        <v>117</v>
-      </c>
-      <c r="C36" t="s">
-        <v>115</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>20</v>
@@ -1422,16 +1428,17 @@
       <c r="G36" s="1">
         <v>24</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>119</v>
-      </c>
-      <c r="B37" t="s">
-        <v>121</v>
-      </c>
-      <c r="C37" t="s">
-        <v>122</v>
+      <c r="H36" s="4"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>20</v>
@@ -1443,18 +1450,19 @@
         <v>21</v>
       </c>
       <c r="G37" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>120</v>
-      </c>
-      <c r="B38" t="s">
-        <v>123</v>
-      </c>
-      <c r="C38" t="s">
-        <v>47</v>
+        <v>6</v>
+      </c>
+      <c r="H37" s="4"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>20</v>
@@ -1463,13 +1471,14 @@
         <v>1</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="G38" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+      <c r="H38" s="4"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>124</v>
       </c>
@@ -1492,10 +1501,33 @@
         <v>10</v>
       </c>
     </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>126</v>
+      </c>
+      <c r="B40" t="s">
+        <v>127</v>
+      </c>
+      <c r="C40" t="s">
+        <v>128</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" s="1">
+        <v>1</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G40" s="1">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H35">
-      <sortCondition ref="A1"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H40">
+      <sortCondition ref="B1"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/AppLogSolutionLocale/dati/tabella_aggiornamento_articoli.xlsx
+++ b/AppLogSolutionLocale/dati/tabella_aggiornamento_articoli.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\App\AppLogSolutionLocale\dati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA795717-8B57-409A-A735-4DFF177DCC3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2675579D-E585-4A04-A50A-DD474DDAC06A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4968" yWindow="2100" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Articoli" sheetId="1" r:id="rId1"/>
@@ -774,7 +774,7 @@
     <col min="2" max="2" width="47.88671875" customWidth="1"/>
     <col min="3" max="3" width="38" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
     <col min="8" max="8" width="14" style="3" customWidth="1"/>

--- a/AppLogSolutionLocale/dati/tabella_aggiornamento_articoli.xlsx
+++ b/AppLogSolutionLocale/dati/tabella_aggiornamento_articoli.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\App\AppLogSolutionLocale\dati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2675579D-E585-4A04-A50A-DD474DDAC06A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F40CD38A-703B-4EE3-A1D9-17143B1C0CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4968" yWindow="2100" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13344" yWindow="132" windowWidth="16860" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Articoli" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="131">
   <si>
     <t>Codice</t>
   </si>
@@ -411,6 +411,12 @@
   </si>
   <si>
     <t>12 Porzioni / Collo</t>
+  </si>
+  <si>
+    <t>NE-M-BI-L3-NI</t>
+  </si>
+  <si>
+    <t>Mousse di Nettarina biologica</t>
   </si>
 </sst>
 </file>
@@ -767,7 +773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.33203125" customWidth="1"/>
@@ -1524,6 +1530,29 @@
         <v>12</v>
       </c>
     </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>129</v>
+      </c>
+      <c r="B41" t="s">
+        <v>130</v>
+      </c>
+      <c r="C41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" s="1">
+        <v>1</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G41" s="1">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H40">
